--- a/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
+++ b/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
@@ -327,7 +327,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" val="0"/>
+              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1064,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45373</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1096,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45376</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1128,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45376</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1160,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45378</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1192,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45378</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>

--- a/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
+++ b/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
@@ -13,9 +13,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD10000.1-OCT'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -106,12 +106,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,7 +327,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -612,9 +612,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
     <col min="2" max="2" width="16.5703125" style="12" customWidth="1"/>
@@ -622,14 +622,14 @@
     <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
     </row>
-    <row r="7" spans="2:3" ht="16.5">
+    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
@@ -637,7 +637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="16.5">
+    <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>8</v>
       </c>
@@ -645,7 +645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="16.5">
+    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
@@ -653,7 +653,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="16.5">
+    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
@@ -661,7 +661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="16.5">
+    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>11</v>
       </c>
@@ -669,7 +669,7 @@
         <v>9863328343</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="16.5">
+    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>12</v>
       </c>
@@ -677,7 +677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="16.5">
+    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>13</v>
       </c>
@@ -685,7 +685,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="16.5">
+    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>14</v>
       </c>
@@ -693,47 +693,47 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="16.5">
+    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="2:3" ht="16.5">
+    <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="14"/>
     </row>
-    <row r="17" spans="2:3" ht="16.5">
+    <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="22"/>
     </row>
-    <row r="19" spans="2:3" ht="16.5">
+    <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
-    <row r="21" spans="2:3" ht="16.5">
+    <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="22"/>
     </row>
-    <row r="22" spans="2:3" ht="16.5">
+    <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
-    <row r="23" spans="2:3" ht="16.5">
+    <row r="23" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="15"/>
     </row>
-    <row r="24" spans="2:3" ht="16.5">
+    <row r="24" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
     </row>
-    <row r="25" spans="2:3" ht="16.5">
+    <row r="25" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>19</v>
       </c>
@@ -741,17 +741,17 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="16.5">
+    <row r="26" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="27" spans="2:3" ht="16.5">
+    <row r="27" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="15"/>
     </row>
-    <row r="28" spans="2:3" ht="16.5">
+    <row r="28" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
     </row>
@@ -767,9 +767,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.140625" style="2" customWidth="1"/>
@@ -789,7 +789,7 @@
     <col min="17" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,11 +821,11 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4000</v>
+        <v>5900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,11 +854,11 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8000</v>
+        <v>6100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:16" ht="16.5" customHeight="1">
+    <row r="3" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -896,7 +896,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="16.5" customHeight="1">
+    <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -934,7 +934,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="16.5" customHeight="1">
+    <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="16.5" customHeight="1">
+    <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1010,7 +1010,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1048,7 +1048,7 @@
       <c r="O7" s="4"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="16.5" customHeight="1">
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1086,7 +1086,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="16.5" customHeight="1">
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1124,7 +1124,7 @@
       <c r="O9" s="4"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1">
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1162,7 +1162,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="16.5" customHeight="1">
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1200,7 +1200,7 @@
       <c r="O11" s="4"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1">
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1238,7 +1238,7 @@
       <c r="O12" s="4"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="16.5" customHeight="1">
+    <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1254,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1270,7 +1276,7 @@
       <c r="O13" s="4"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="16.5" customHeight="1">
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1286,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1302,7 +1314,7 @@
       <c r="O14" s="4"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="16.5" customHeight="1">
+    <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1318,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1334,7 +1352,7 @@
       <c r="O15" s="4"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="16.5" customHeight="1">
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1350,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1366,7 +1390,7 @@
       <c r="O16" s="4"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="16.5" customHeight="1">
+    <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1382,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1398,7 +1428,7 @@
       <c r="O17" s="4"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" ht="16.5" customHeight="1">
+    <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1414,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1430,7 +1466,7 @@
       <c r="O18" s="4"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" ht="16.5" customHeight="1">
+    <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1446,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1462,7 +1504,7 @@
       <c r="O19" s="4"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="16.5" customHeight="1">
+    <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1478,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1494,7 +1542,7 @@
       <c r="O20" s="4"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="16.5" customHeight="1">
+    <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1510,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45398</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1526,7 +1580,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="1:16" ht="16.5" customHeight="1">
+    <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1542,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1558,7 +1618,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="1:16" ht="16.5" customHeight="1">
+    <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1574,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1590,7 +1656,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="16.5" customHeight="1">
+    <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1606,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1622,7 +1694,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" ht="16.5" customHeight="1">
+    <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1638,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1654,7 +1732,7 @@
       <c r="O25" s="4"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" ht="16.5" customHeight="1">
+    <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1670,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1686,7 +1770,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" ht="16.5" customHeight="1">
+    <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1702,9 +1786,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1718,7 +1808,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" ht="16.5" customHeight="1">
+    <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1734,9 +1824,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1750,7 +1846,7 @@
       <c r="O28" s="4"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" ht="16.5" customHeight="1">
+    <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1766,9 +1862,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1782,7 +1884,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" ht="16.5" customHeight="1">
+    <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1798,9 +1900,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1814,7 +1922,7 @@
       <c r="O30" s="4"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1">
+    <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1830,9 +1938,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45414</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1846,7 +1960,7 @@
       <c r="O31" s="4"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1">
+    <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>

--- a/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
+++ b/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5900</v>
+        <v>6600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6100</v>
+        <v>5400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -962,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1000,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1038,9 +1062,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1076,9 +1106,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45472</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1976,9 +2012,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45472</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
+++ b/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6600</v>
+        <v>7600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1150,9 +1150,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1188,9 +1194,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1226,9 +1238,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1264,9 +1282,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1302,9 +1326,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1340,9 +1370,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1378,9 +1414,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1416,9 +1458,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1454,9 +1502,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1492,9 +1546,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>

--- a/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
+++ b/LoanOfficer-A/2023/23 Loanee-Mona -.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7600</v>
+        <v>9500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45534</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45534</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45534</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45534</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1074,9 +1098,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45534</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1590,9 +1620,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45508</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1628,9 +1664,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45508</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1666,9 +1708,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45508</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1704,9 +1752,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45508</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1742,9 +1796,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45528</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1780,9 +1840,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45528</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1818,9 +1884,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45528</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1856,9 +1928,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45528</v>
+      </c>
+      <c r="K26" s="4">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1894,9 +1972,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45528</v>
+      </c>
+      <c r="K27" s="4">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1932,9 +2016,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45534</v>
+      </c>
+      <c r="K28" s="4">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1970,9 +2060,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45534</v>
+      </c>
+      <c r="K29" s="4">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -2008,9 +2104,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45534</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -2046,9 +2148,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45534</v>
+      </c>
+      <c r="K31" s="4">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2084,9 +2192,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45534</v>
+      </c>
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>
